--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0003T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0003T0006Z000C1N10_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.53608623995508</v>
+        <v>9.512114013992701</v>
       </c>
       <c r="D2" t="n">
-        <v>57.67298114950069</v>
+        <v>9.371859436793862</v>
       </c>
       <c r="E2" t="n">
-        <v>16.05211884352655</v>
+        <v>2.608469312073064</v>
       </c>
       <c r="F2" t="n">
-        <v>16.45238252504251</v>
+        <v>2.673512160319407</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.83462999011915</v>
+        <v>8.423127373394363</v>
       </c>
       <c r="D3" t="n">
-        <v>50.92107224404862</v>
+        <v>8.274674239657902</v>
       </c>
       <c r="E3" t="n">
-        <v>16.05211884352655</v>
+        <v>2.608469312073064</v>
       </c>
       <c r="F3" t="n">
-        <v>16.45238252504251</v>
+        <v>2.673512160319407</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>56.37382677822693</v>
+        <v>9.160746851461877</v>
       </c>
       <c r="D4" t="n">
-        <v>55.9242852704757</v>
+        <v>9.087696356452302</v>
       </c>
       <c r="E4" t="n">
-        <v>16.05211884352655</v>
+        <v>2.608469312073064</v>
       </c>
       <c r="F4" t="n">
-        <v>16.45238252504251</v>
+        <v>2.673512160319407</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.98596182676129</v>
+        <v>5.68521879684871</v>
       </c>
       <c r="D5" t="n">
-        <v>34.27187265610944</v>
+        <v>5.569179306617785</v>
       </c>
       <c r="E5" t="n">
-        <v>16.05211884352655</v>
+        <v>2.608469312073064</v>
       </c>
       <c r="F5" t="n">
-        <v>16.45238252504251</v>
+        <v>2.673512160319407</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>7.892016417623784</v>
+        <v>1.282452667863865</v>
       </c>
       <c r="D6" t="n">
-        <v>7.113214156751165</v>
+        <v>1.155897300472064</v>
       </c>
       <c r="E6" t="n">
-        <v>16.05211884352655</v>
+        <v>2.608469312073064</v>
       </c>
       <c r="F6" t="n">
-        <v>16.45238252504251</v>
+        <v>2.673512160319407</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.92660945022849</v>
+        <v>4.37557403566213</v>
       </c>
       <c r="D7" t="n">
-        <v>26.89961388177317</v>
+        <v>4.37118725578814</v>
       </c>
       <c r="E7" t="n">
-        <v>16.05211884352655</v>
+        <v>2.608469312073064</v>
       </c>
       <c r="F7" t="n">
-        <v>16.45238252504251</v>
+        <v>2.673512160319407</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>47.30310697781967</v>
+        <v>7.686754883895698</v>
       </c>
       <c r="D8" t="n">
-        <v>47.35759271701823</v>
+        <v>7.695608816515462</v>
       </c>
       <c r="E8" t="n">
-        <v>16.05211884352655</v>
+        <v>2.608469312073064</v>
       </c>
       <c r="F8" t="n">
-        <v>16.45238252504251</v>
+        <v>2.673512160319407</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>38.22904640187381</v>
+        <v>6.212220040304494</v>
       </c>
       <c r="D9" t="n">
-        <v>20.93740867879248</v>
+        <v>3.402328910303778</v>
       </c>
       <c r="E9" t="n">
-        <v>16.05211884352655</v>
+        <v>2.608469312073064</v>
       </c>
       <c r="F9" t="n">
-        <v>16.45238252504251</v>
+        <v>2.673512160319407</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.45034523107562</v>
+        <v>4.623181100049789</v>
       </c>
       <c r="D10" t="n">
-        <v>27.54784210129953</v>
+        <v>4.476524341461174</v>
       </c>
       <c r="E10" t="n">
-        <v>16.05211884352655</v>
+        <v>2.608469312073064</v>
       </c>
       <c r="F10" t="n">
-        <v>16.45238252504251</v>
+        <v>2.673512160319407</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>12.44822708236869</v>
+        <v>2.022836900884913</v>
       </c>
       <c r="D11" t="n">
-        <v>11.87749319312464</v>
+        <v>1.930092643882755</v>
       </c>
       <c r="E11" t="n">
-        <v>16.05211884352655</v>
+        <v>2.608469312073064</v>
       </c>
       <c r="F11" t="n">
-        <v>16.45238252504251</v>
+        <v>2.673512160319407</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>39.70408389625566</v>
+        <v>6.451913633141545</v>
       </c>
       <c r="D12" t="n">
-        <v>36.45888212202787</v>
+        <v>5.924568344829529</v>
       </c>
       <c r="E12" t="n">
-        <v>16.05211884352655</v>
+        <v>2.608469312073064</v>
       </c>
       <c r="F12" t="n">
-        <v>16.45238252504251</v>
+        <v>2.673512160319407</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>54.42054522315858</v>
+        <v>8.843338598763269</v>
       </c>
       <c r="D13" t="n">
-        <v>51.17873198998306</v>
+        <v>8.316543948372248</v>
       </c>
       <c r="E13" t="n">
-        <v>16.05211884352655</v>
+        <v>2.608469312073064</v>
       </c>
       <c r="F13" t="n">
-        <v>16.45238252504251</v>
+        <v>2.673512160319407</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
